--- a/CHARMS COLGANTES DISNEY.xlsx
+++ b/CHARMS COLGANTES DISNEY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\CATALOGO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EFCB0AE-E816-494B-B492-83D38AB527EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6600BD42-7644-468F-B60C-7CB356CC4460}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{44B837E0-01FB-47FB-9746-0A32C4320ACA}"/>
   </bookViews>
@@ -120,7 +120,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -149,6 +149,12 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor rgb="FFF5F5F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -180,7 +186,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -227,6 +233,9 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -9838,49 +9847,6 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>809625</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>771525</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="225" name="image218.jpg">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B0A72CB2-3E57-42A7-9977-AB2102409948}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId223" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="685800" y="42319575"/>
-          <a:ext cx="733425" cy="714375"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
       <xdr:colOff>47625</xdr:colOff>
       <xdr:row>62</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
@@ -9903,7 +9869,7 @@
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId224" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId223" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -9946,7 +9912,7 @@
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId225" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId224" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -9989,7 +9955,7 @@
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId226" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId225" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -10032,7 +9998,7 @@
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId227" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId226" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -10075,7 +10041,7 @@
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId228" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId227" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -10118,7 +10084,7 @@
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId229" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId228" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -10161,7 +10127,7 @@
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId230" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId229" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -10204,7 +10170,7 @@
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId231" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId230" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -10247,7 +10213,7 @@
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId232" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId231" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -10255,49 +10221,6 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="704850" y="35013900"/>
-          <a:ext cx="733425" cy="714375"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>53</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>809625</xdr:colOff>
-      <xdr:row>53</xdr:row>
-      <xdr:rowOff>742950</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="235" name="image229.jpg">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8D5BCF7A-23F2-4A75-9BDB-B59EBAE1DF8E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId233" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="685800" y="34194750"/>
           <a:ext cx="733425" cy="714375"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -10333,7 +10256,7 @@
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId234" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId232" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -10376,7 +10299,7 @@
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId235" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId233" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -10419,7 +10342,7 @@
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId236" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId234" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -10462,7 +10385,7 @@
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId237" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId235" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -10505,7 +10428,7 @@
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId238" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId236" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -10548,7 +10471,7 @@
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId239" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId237" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -10591,7 +10514,7 @@
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId240" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId238" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -10634,7 +10557,7 @@
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId241" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId239" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -10677,7 +10600,7 @@
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId242" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId240" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -10720,7 +10643,7 @@
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId243" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId241" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -10763,7 +10686,7 @@
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId244" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId242" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -10806,7 +10729,7 @@
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId245" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId243" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -10849,7 +10772,7 @@
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId246" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId244" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -10892,7 +10815,7 @@
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId247" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId245" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -10935,7 +10858,7 @@
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId248" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId246" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -10978,7 +10901,7 @@
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId249" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId247" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -11021,7 +10944,7 @@
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId250" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId248" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -11064,7 +10987,7 @@
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId251" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId249" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -11107,7 +11030,7 @@
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId252" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId250" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -11150,7 +11073,7 @@
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId253" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId251" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -11193,7 +11116,7 @@
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId254" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId252" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -11236,7 +11159,7 @@
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId255" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId253" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -11279,7 +11202,7 @@
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId256" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId254" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -11322,7 +11245,7 @@
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId257" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId255" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -11365,7 +11288,7 @@
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId258" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId256" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -11408,7 +11331,7 @@
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId259" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId257" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -11451,7 +11374,7 @@
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId260" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId258" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -11494,7 +11417,7 @@
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId261" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId259" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -11537,7 +11460,7 @@
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId262" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId260" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -11580,7 +11503,7 @@
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId263" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId261" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -11623,7 +11546,7 @@
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId264" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId262" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -11666,7 +11589,7 @@
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId265" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId263" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -11709,7 +11632,7 @@
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId266" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId264" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -11752,7 +11675,7 @@
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId267" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId265" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -11795,7 +11718,7 @@
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId268" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId266" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -11838,7 +11761,7 @@
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId269" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId267" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -11881,7 +11804,7 @@
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId270" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId268" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -11924,7 +11847,7 @@
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId271" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId269" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -11967,7 +11890,7 @@
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId272" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId270" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -12010,7 +11933,7 @@
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId273" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId271" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -12053,7 +11976,7 @@
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId274" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId272" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -12098,7 +12021,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId275"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId273"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -12142,7 +12065,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId276"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId274"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -12186,7 +12109,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId277"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId275"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -12230,7 +12153,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId278"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId276"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -12274,7 +12197,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId279"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId277"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -12318,7 +12241,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId280"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId278"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -12362,7 +12285,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId281"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId279"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -12406,7 +12329,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId282"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId280"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -12450,7 +12373,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId283"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId281"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -12494,7 +12417,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId284"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId282"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -12538,7 +12461,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId285"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId283"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -12582,7 +12505,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId286"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId284"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -12591,6 +12514,94 @@
         <a:xfrm>
           <a:off x="742950" y="204787"/>
           <a:ext cx="623887" cy="721720"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>295276</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>65459</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>642938</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>800191</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="289" name="Imagen 288">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED53664D-3F24-059E-A003-5C26D0053A03}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId285"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="904876" y="42327884"/>
+          <a:ext cx="347662" cy="734732"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>276804</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>666750</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>755244</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="235" name="Imagen 234">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8BD1F656-5BAA-BA49-524B-8CB1BA980245}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId286"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="886404" y="50415825"/>
+          <a:ext cx="389946" cy="698094"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -13188,7 +13199,7 @@
       <c r="K10" s="10"/>
     </row>
     <row r="11" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="6">
+      <c r="A11" s="16">
         <v>276</v>
       </c>
       <c r="B11" s="7"/>
@@ -13601,7 +13612,7 @@
       <c r="K25" s="10"/>
     </row>
     <row r="26" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="6">
+      <c r="A26" s="16">
         <v>261</v>
       </c>
       <c r="B26" s="12"/>
@@ -14361,10 +14372,10 @@
       <c r="K53" s="10"/>
     </row>
     <row r="54" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="6">
+      <c r="A54" s="16">
         <v>233</v>
       </c>
-      <c r="B54" s="11"/>
+      <c r="B54" s="12"/>
       <c r="C54" s="8">
         <v>3.42</v>
       </c>
@@ -14633,10 +14644,10 @@
       <c r="K63" s="10"/>
     </row>
     <row r="64" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="6">
+      <c r="A64" s="16">
         <v>223</v>
       </c>
-      <c r="B64" s="11"/>
+      <c r="B64" s="12"/>
       <c r="C64" s="8">
         <v>3.16</v>
       </c>
